--- a/Excel-files/purchase_activateBulk.xlsx
+++ b/Excel-files/purchase_activateBulk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS01503\Documents\load testing Script-BSS\Excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B3EB98-2162-4D06-BEEB-57D434A59F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB2A405-17EE-4BFC-88B9-F6DC26CA1A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase (Activate)" sheetId="1" r:id="rId1"/>
@@ -170,29 +170,29 @@
     <t>false</t>
   </si>
   <si>
-    <t>SID2609000935</t>
-  </si>
-  <si>
     <t>30 days</t>
   </si>
   <si>
     <t>SV2600069</t>
   </si>
   <si>
-    <t>SID2609000934</t>
-  </si>
-  <si>
-    <t>SID2609000933</t>
-  </si>
-  <si>
-    <t>SID2609000932</t>
+    <t>SID2609000950</t>
+  </si>
+  <si>
+    <t>SID2609000949</t>
+  </si>
+  <si>
+    <t>SID2609000947</t>
+  </si>
+  <si>
+    <t>SID2609000948</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -220,6 +220,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -235,8 +242,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -264,17 +271,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -282,17 +283,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -771,19 +778,19 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C2" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46304</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
       </c>
       <c r="G2" t="s">
         <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
         <v>37</v>
@@ -794,56 +801,56 @@
         <v>41</v>
       </c>
       <c r="B3" s="2">
-        <v>46304</v>
+        <v>46274</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
         <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="2">
-        <v>46304</v>
+        <v>46274</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
         <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B5" s="2">
-        <v>46304</v>
+        <v>46274</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
         <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L5" t="s">
         <v>37</v>
